--- a/data/test/structured/case_relevant_call_records.xlsx
+++ b/data/test/structured/case_relevant_call_records.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="call_records" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,16 +551,18 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2024-08-12 02:16:00</t>
+          <t>2008-08-12 02:16:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2024-08-12 02:16:00</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>72</v>
+          <t>2008-08-12 02:16:00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -641,16 +643,18 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2024-08-12 02:31:00</t>
+          <t>2008-08-12 02:31:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2024-08-12 02:31:00</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>188</v>
+          <t>2008-08-12 02:31:00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -731,16 +735,18 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2024-08-12 08:42:00</t>
+          <t>2008-08-12 08:42:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2024-08-12 08:42:00</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>231</v>
+          <t>2008-08-12 08:42:00</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -821,16 +827,18 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2024-08-12 09:05:00</t>
+          <t>2008-08-12 09:05:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2024-08-12 09:05:00</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>164</v>
+          <t>2008-08-12 09:05:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -911,16 +919,18 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2024-08-12 09:18:00</t>
+          <t>2008-08-12 09:18:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2024-08-12 09:18:00</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>93</v>
+          <t>2008-08-12 09:18:00</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1001,16 +1011,18 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2024-08-16 09:56:00</t>
+          <t>2008-08-16 09:56:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2024-08-16 09:56:00</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>66</v>
+          <t>2008-08-16 09:56:00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1091,16 +1103,18 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2024-08-16 10:04:00</t>
+          <t>2008-08-16 10:04:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2024-08-16 10:04:00</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>58</v>
+          <t>2008-08-16 10:04:00</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1181,16 +1195,18 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2024-08-16 10:09:00</t>
+          <t>2008-08-16 10:09:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2024-08-16 10:09:00</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>74</v>
+          <t>2008-08-16 10:09:00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1271,16 +1287,18 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2024-08-17 15:18:00</t>
+          <t>2008-08-17 15:18:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2024-08-17 15:18:00</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>81</v>
+          <t>2008-08-17 15:18:00</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1361,16 +1379,18 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2024-08-18 09:36:00</t>
+          <t>2008-08-18 09:36:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2024-08-18 09:36:00</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>49</v>
+          <t>2008-08-18 09:36:00</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1451,16 +1471,18 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2024-08-18 13:52:00</t>
+          <t>2008-08-18 13:52:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2024-08-18 13:52:00</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>55</v>
+          <t>2008-08-18 13:52:00</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1541,16 +1563,18 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2024-08-19 16:12:00</t>
+          <t>2008-08-19 16:12:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2024-08-19 16:12:00</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>112</v>
+          <t>2008-08-19 16:12:00</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1631,16 +1655,18 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2024-08-21 10:19:00</t>
+          <t>2008-08-21 10:19:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2024-08-21 10:19:00</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>37</v>
+          <t>2008-08-21 10:19:00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1721,16 +1747,18 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2024-08-16 14:24:00</t>
+          <t>2008-08-16 14:24:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2024-08-16 14:24:00</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>143</v>
+          <t>2008-08-16 14:24:00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1811,16 +1839,18 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2024-08-17 11:08:00</t>
+          <t>2008-08-17 11:08:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2024-08-17 11:08:00</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>219</v>
+          <t>2008-08-17 11:08:00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1901,16 +1931,18 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2024-08-17 11:33:00</t>
+          <t>2008-08-17 11:33:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2024-08-17 11:33:00</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>132</v>
+          <t>2008-08-17 11:33:00</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1991,16 +2023,18 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2024-09-05 17:21:00</t>
+          <t>2008-09-05 17:21:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2024-09-05 17:21:00</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>177</v>
+          <t>2008-09-05 17:21:00</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2081,16 +2115,18 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2024-09-06 08:57:00</t>
+          <t>2008-09-06 08:57:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2024-09-06 08:57:00</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>64</v>
+          <t>2008-09-06 08:57:00</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2171,16 +2207,18 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2024-09-06 09:12:00</t>
+          <t>2008-09-06 09:12:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2024-09-06 09:12:00</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>71</v>
+          <t>2008-09-06 09:12:00</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2261,16 +2299,18 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2024-09-06 09:43:00</t>
+          <t>2008-09-06 09:43:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2024-09-06 09:43:00</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>59</v>
+          <t>2008-09-06 09:43:00</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2351,16 +2391,18 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2024-09-07 16:20:00</t>
+          <t>2008-09-07 16:20:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2024-09-07 16:20:00</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>118</v>
+          <t>2008-09-07 16:20:00</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>

--- a/data/test/structured/case_relevant_call_records.xlsx
+++ b/data/test/structured/case_relevant_call_records.xlsx
@@ -551,12 +551,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2008-08-12 02:16:00</t>
+          <t>2024-08-12 02:16:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2008-08-12 02:16:00</t>
+          <t>2024-08-12 02:16:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2008-08-12 02:31:00</t>
+          <t>2024-08-12 02:31:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2008-08-12 02:31:00</t>
+          <t>2024-08-12 02:31:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2008-08-12 08:42:00</t>
+          <t>2024-08-12 08:42:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2008-08-12 08:42:00</t>
+          <t>2024-08-12 08:42:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2008-08-12 09:05:00</t>
+          <t>2024-08-12 09:05:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2008-08-12 09:05:00</t>
+          <t>2024-08-12 09:05:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2008-08-12 09:18:00</t>
+          <t>2024-08-12 09:18:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2008-08-12 09:18:00</t>
+          <t>2024-08-12 09:18:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2008-08-16 09:56:00</t>
+          <t>2024-08-16 09:56:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2008-08-16 09:56:00</t>
+          <t>2024-08-16 09:56:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2008-08-16 10:04:00</t>
+          <t>2024-08-16 10:04:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2008-08-16 10:04:00</t>
+          <t>2024-08-16 10:04:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2008-08-16 10:09:00</t>
+          <t>2024-08-16 10:09:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2008-08-16 10:09:00</t>
+          <t>2024-08-16 10:09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2008-08-17 15:18:00</t>
+          <t>2024-08-17 15:18:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2008-08-17 15:18:00</t>
+          <t>2024-08-17 15:18:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2008-08-18 09:36:00</t>
+          <t>2024-08-18 09:36:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2008-08-18 09:36:00</t>
+          <t>2024-08-18 09:36:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1471,12 +1471,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2008-08-18 13:52:00</t>
+          <t>2024-08-18 13:52:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2008-08-18 13:52:00</t>
+          <t>2024-08-18 13:52:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2008-08-19 16:12:00</t>
+          <t>2024-08-19 16:12:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2008-08-19 16:12:00</t>
+          <t>2024-08-19 16:12:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2008-08-21 10:19:00</t>
+          <t>2024-08-21 10:19:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2008-08-21 10:19:00</t>
+          <t>2024-08-21 10:19:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2008-08-16 14:24:00</t>
+          <t>2024-08-16 14:24:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2008-08-16 14:24:00</t>
+          <t>2024-08-16 14:24:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2008-08-17 11:08:00</t>
+          <t>2024-08-17 11:08:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2008-08-17 11:08:00</t>
+          <t>2024-08-17 11:08:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2008-08-17 11:33:00</t>
+          <t>2024-08-17 11:33:00</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2008-08-17 11:33:00</t>
+          <t>2024-08-17 11:33:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2008-09-05 17:21:00</t>
+          <t>2024-09-05 17:21:00</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2008-09-05 17:21:00</t>
+          <t>2024-09-05 17:21:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2008-09-06 08:57:00</t>
+          <t>2024-09-06 08:57:00</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2008-09-06 08:57:00</t>
+          <t>2024-09-06 08:57:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2008-09-06 09:12:00</t>
+          <t>2024-09-06 09:12:00</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2008-09-06 09:12:00</t>
+          <t>2024-09-06 09:12:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2008-09-06 09:43:00</t>
+          <t>2024-09-06 09:43:00</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2008-09-06 09:43:00</t>
+          <t>2024-09-06 09:43:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2008-09-07 16:20:00</t>
+          <t>2024-09-07 16:20:00</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2008-09-07 16:20:00</t>
+          <t>2024-09-07 16:20:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
